--- a/ao/cyrce-biot2-normandie/03_BUDGET.xlsx
+++ b/ao/cyrce-biot2-normandie/03_BUDGET.xlsx
@@ -9,9 +9,11 @@
   </bookViews>
   <sheets>
     <sheet name="Hypothèses" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="CYRCE" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="BIOT2" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Synthèse" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="CYRCE_A" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="CYRCE_B" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="BIOT2_A" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="BIOT2_B" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Synthèse" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -22,7 +24,7 @@
 </workbook>
 </file>
 
-<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
     <author>Unknown Author</author>
@@ -45,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="112">
   <si>
     <t xml:space="preserve">LÉGENDE : cellules bleues = valeurs modifiables (inputs) — cellules noires = formules.</t>
   </si>
@@ -122,7 +124,7 @@
     <t xml:space="preserve">Comédien image (hors droits)</t>
   </si>
   <si>
-    <t xml:space="preserve">BPU IDFM Grille Coûts Production — Marché / CCN</t>
+    <t xml:space="preserve">Cachet minimum tournage "Publicité &amp; contenus de marque" ≈ 534 €/j (grilles syndicales 2025, hors droits de diffusion) — retenu au plancher conventionnel, pas de marge au-dessus</t>
   </si>
   <si>
     <t xml:space="preserve">Coefficient intermittent (charges Congés Spectacles)</t>
@@ -140,42 +142,99 @@
     <t xml:space="preserve">BPU IDFM Grille Coûts Production — adapté à une équipe resserrée, décors lumineux naturels (bureaux/coworking)</t>
   </si>
   <si>
-    <t xml:space="preserve">Déplacement Normandie (équipe resserrée, par tournage)</t>
+    <t xml:space="preserve">Transport aller-retour par personne (train/route, Paris-Normandie)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">€/pers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimation marché — trajet Paris-Normandie (ville non arrêtée), billet SNCF ou route, aller-retour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pilotage (% charge de production)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Méthodologie interne — session CNES/COMETES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assurance production (matériel, annulation, couverture tournage)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPU IDFM Grille Coûts Production — obligatoire pour tout projet avec tournage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provision imprévus (météo, retakes, prolongation)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taux standard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enveloppe budgétaire client (TTC)</t>
   </si>
   <si>
     <t xml:space="preserve">€</t>
   </si>
   <si>
-    <t xml:space="preserve">Estimation révisée — transport + logistique équipe de 4 pers., 1,5 jour</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pilotage (% charge de production)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Méthodologie interne — session CNES/COMETES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assurance production (RC Pro, matériel, annulation)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BPU IDFM Grille Coûts Production — obligatoire pour tout projet avec tournage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Provision imprévus (météo, retakes, prolongation)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taux standard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enveloppe budgétaire client (TTC)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cahier des charges — Agence Régionale de l'Orientation et des Métiers de Normandie</t>
   </si>
   <si>
+    <t xml:space="preserve">Nuitée hôtel par personne (standard province, petit-déj compris)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">€/nuit/pers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimation marché — hôtel budget/pro en province</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per diem repas par personne et par jour (déjeuner + dîner)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">€/jour/pers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barème URSSAF frais professionnels 2026 — indemnité repas, base 2 repas/jour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Location kit lumière 3 points (LED, softbox, pieds)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimation marché — kit LED 3 points (type Aputure/Godox), indispensable sur les deux scénarios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">— SCÉNARIO A : postes et taux additionnels (équipe complète / tarifs standards, non compressés) —</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1er Assistant réalisateur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Machiniste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chef électricien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Location kit tournage lourd / multicam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPU IDFM Grille Coûts Production — équipe complète, dispositif lumière/son renforcé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maquilleuse / Styliste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimation marché — TJM freelance maquillage/coiffure/stylisme plateau, au-dessus du minimum conventionnel CCPA (155-250 €/j film institutionnel/TV, IDCC 2642)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fournitures maquillage/coiffure (forfait, hors garde-robe)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimation interne — consommables maquillage/coiffure (produits, accessoires) ; garde-robe non chiffrée, puisée dans les vêtements personnels des comédiens</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jours / Quantité</t>
   </si>
   <si>
@@ -200,7 +259,7 @@
     <t xml:space="preserve">Casting — recherche &amp; coordination (interne)</t>
   </si>
   <si>
-    <t xml:space="preserve">TOURNAGE (1,5 jour, équipe resserrée)</t>
+    <t xml:space="preserve">TOURNAGE (2 jours, équipe complète — SCÉNARIO A, 8 postes, kit lourd/multicam)</t>
   </si>
   <si>
     <t xml:space="preserve">Réalisateur</t>
@@ -215,13 +274,22 @@
     <t xml:space="preserve">Supervision interne (présence tournage)</t>
   </si>
   <si>
-    <t xml:space="preserve">Comédiens — jours-comédien (2 comédiens × 1,5j)</t>
+    <t xml:space="preserve">Comédiens — jours-comédien (2 comédiens × 2j)</t>
   </si>
   <si>
     <t xml:space="preserve">Comédiens — charges Congés Spectacles</t>
   </si>
   <si>
-    <t xml:space="preserve">Déplacement Normandie (équipe resserrée)</t>
+    <t xml:space="preserve">Transport aller-retour équipe (8 pers.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hébergement — nuitées équipe (8 pers. × 2 nuits)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repas — per diem équipe (8 pers. × 3 jours)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fournitures maquillage/coiffure (forfait)</t>
   </si>
   <si>
     <t xml:space="preserve">POST-PRODUCTION</t>
@@ -257,22 +325,64 @@
     <t xml:space="preserve">TOTAL coût de revient (HT)</t>
   </si>
   <si>
+    <t xml:space="preserve">TOURNAGE (1,5 jour, équipe resserrée — SCÉNARIO B, contrainte budget AO)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comédiens — jours-comédien (2 comédiens × 1.5j)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transport aller-retour équipe (4 pers.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hébergement — nuitées équipe (4 pers. × 2 nuits)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repas — per diem équipe (4 pers. × 3 jours)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Montant</t>
   </si>
   <si>
+    <t xml:space="preserve">SCÉNARIO A — Tarifs internes (équipe complète, sans compression)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Total coût de revient CYRCE (HT)</t>
   </si>
   <si>
     <t xml:space="preserve">Total coût de revient BIOT2 (HT)</t>
   </si>
   <si>
-    <t xml:space="preserve">TOTAL coût de revient global (HT)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOTAL coût de revient (TTC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Écart (marge disponible, avant marge commerciale OPS)</t>
+    <t xml:space="preserve">TOTAL Scénario A — coût de revient global (HT)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL Scénario A (TTC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCÉNARIO B — Contrainte budget AO (resserré)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL Scénario B — coût de revient global (HT)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL Scénario B (TTC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMPARATIF AU BUDGET CLIENT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marge disponible Scénario B vs enveloppe (avant marge commerciale OPS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ÉCART A → B — RISQUE / MANQUE À GAGNER SI SCÉNARIO B RETENU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Écart HT (coût réel équipe complète − coût scénario contraint)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Écart TTC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Écart en % du coût réel Scénario A (HT)</t>
   </si>
 </sst>
 </file>
@@ -349,7 +459,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -360,6 +470,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD9D9D9"/>
         <bgColor rgb="FFC0C0C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -397,8 +513,48 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="25">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -406,7 +562,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -414,31 +570,39 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -479,7 +643,7 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFFFF2CC"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
@@ -702,304 +866,444 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="82"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="6" t="n">
         <v>1200</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="6" t="n">
         <v>550</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>480</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>480</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>600</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="6" t="n">
         <v>400</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="5" t="n">
-        <v>600</v>
-      </c>
-      <c r="C14" s="4" t="s">
+      <c r="B14" s="6" t="n">
+        <v>534</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="7" t="n">
         <v>0.154</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="6" t="n">
         <v>700</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C17" s="4" t="s">
+      <c r="B17" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="7" t="n">
         <v>0.15</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="7" t="n">
         <v>0.03</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="7" t="n">
         <v>0.05</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="7" t="n">
         <v>0.2</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="5" t="n">
+      <c r="B22" s="6" t="n">
         <v>40000</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D22" s="1" t="s">
+      <c r="C22" s="5" t="s">
         <v>42</v>
       </c>
+      <c r="D22" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="9" t="n">
+        <v>95</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" s="6"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="2"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>450</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>340</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" s="9" t="n">
+        <v>430</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" s="9" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B31" s="9" t="n">
+        <v>400</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B32" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="10"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1017,383 +1321,510 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>45</v>
+      <c r="B1" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
-        <v>46</v>
+      <c r="A2" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B3" s="8" t="n">
+      <c r="A3" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="C3" s="9" t="n">
+      <c r="C3" s="15" t="n">
         <f aca="false">Hypothèses!$B$13</f>
         <v>200</v>
       </c>
-      <c r="D3" s="9" t="n">
+      <c r="D3" s="16" t="n">
         <f aca="false">B3*C3</f>
         <v>300</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B4" s="8" t="n">
+      <c r="A4" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="9" t="n">
+      <c r="C4" s="15" t="n">
         <f aca="false">Hypothèses!$B$12</f>
         <v>400</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="16" t="n">
         <f aca="false">B4*C4</f>
         <v>400</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B5" s="8" t="n">
+      <c r="A5" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="15" t="n">
         <f aca="false">Hypothèses!$B$7</f>
         <v>300</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="16" t="n">
         <f aca="false">B5*C5</f>
         <v>150</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B6" s="8" t="n">
+      <c r="A6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="15" t="n">
         <f aca="false">Hypothèses!$B$13</f>
         <v>200</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="16" t="n">
         <f aca="false">B6*C6</f>
         <v>200</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>51</v>
+      <c r="A7" s="14" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B8" s="8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C8" s="9" t="n">
+      <c r="A8" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="15" t="n">
         <f aca="false">Hypothèses!$B$4</f>
         <v>1200</v>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="16" t="n">
         <f aca="false">B8*C8</f>
-        <v>1800</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B9" s="8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C9" s="9" t="n">
+      <c r="B9" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="15" t="n">
+        <f aca="false">Hypothèses!$B$27</f>
+        <v>450</v>
+      </c>
+      <c r="D9" s="16" t="n">
+        <f aca="false">B9*C9</f>
+        <v>900</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="15" t="n">
         <f aca="false">Hypothèses!$B$5</f>
         <v>550</v>
       </c>
-      <c r="D9" s="9" t="n">
-        <f aca="false">B9*C9</f>
-        <v>825</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="D10" s="16" t="n">
+        <f aca="false">B10*C10</f>
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C10" s="9" t="n">
+      <c r="B11" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="15" t="n">
         <f aca="false">Hypothèses!$B$6</f>
         <v>500</v>
       </c>
-      <c r="D10" s="9" t="n">
-        <f aca="false">B10*C10</f>
-        <v>750</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="D11" s="16" t="n">
+        <f aca="false">B11*C11</f>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B11" s="8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C11" s="9" t="n">
+      <c r="B12" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="15" t="n">
+        <f aca="false">Hypothèses!$B$28</f>
+        <v>340</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <f aca="false">B12*C12</f>
+        <v>680</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="15" t="n">
+        <f aca="false">Hypothèses!$B$29</f>
+        <v>430</v>
+      </c>
+      <c r="D13" s="16" t="n">
+        <f aca="false">B13*C13</f>
+        <v>860</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="15" t="n">
         <f aca="false">Hypothèses!$B$7</f>
         <v>300</v>
       </c>
-      <c r="D11" s="9" t="n">
-        <f aca="false">B11*C11</f>
-        <v>450</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12" s="8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C12" s="9" t="n">
+      <c r="D14" s="16" t="n">
+        <f aca="false">B14*C14</f>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="15" t="n">
+        <f aca="false">Hypothèses!$B$31</f>
+        <v>400</v>
+      </c>
+      <c r="D15" s="16" t="n">
+        <f aca="false">B15*C15</f>
+        <v>800</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="15" t="n">
         <f aca="false">Hypothèses!$B$13</f>
         <v>200</v>
       </c>
-      <c r="D12" s="9" t="n">
-        <f aca="false">B12*C12</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B13" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C13" s="9" t="n">
+      <c r="D16" s="16" t="n">
+        <f aca="false">B16*C16</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" s="15" t="n">
         <f aca="false">Hypothèses!$B$14</f>
-        <v>600</v>
-      </c>
-      <c r="D13" s="9" t="n">
-        <f aca="false">B13*C13</f>
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C14" s="10" t="n">
+        <v>534</v>
+      </c>
+      <c r="D17" s="16" t="n">
+        <f aca="false">B17*C17</f>
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" s="17" t="n">
         <f aca="false">Hypothèses!$B$15</f>
         <v>0.154</v>
       </c>
-      <c r="D14" s="9" t="n">
-        <f aca="false">D13*C14</f>
-        <v>277.2</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B15" s="8" t="n">
+      <c r="D18" s="16" t="n">
+        <f aca="false">D17*C18</f>
+        <v>328.944</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="C19" s="15" t="n">
+        <f aca="false">Hypothèses!$B$17</f>
+        <v>90</v>
+      </c>
+      <c r="D19" s="16" t="n">
+        <f aca="false">B19*C19</f>
+        <v>720</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="C20" s="15" t="n">
+        <f aca="false">Hypothèses!$B$23</f>
+        <v>95</v>
+      </c>
+      <c r="D20" s="16" t="n">
+        <f aca="false">B20*C20</f>
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="C21" s="15" t="n">
+        <f aca="false">Hypothèses!$B$24</f>
+        <v>40</v>
+      </c>
+      <c r="D21" s="16" t="n">
+        <f aca="false">B21*C21</f>
+        <v>960</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" s="15" t="n">
+        <f aca="false">Hypothèses!$B$30</f>
+        <v>1500</v>
+      </c>
+      <c r="D22" s="16" t="n">
+        <f aca="false">B22*C22</f>
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" s="15" t="n">
+        <f aca="false">Hypothèses!$B$25</f>
+        <v>200</v>
+      </c>
+      <c r="D23" s="16" t="n">
+        <f aca="false">B23*C23</f>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="9" t="n">
-        <f aca="false">Hypothèses!$B$17</f>
-        <v>1000</v>
-      </c>
-      <c r="D15" s="9" t="n">
-        <f aca="false">B15*C15</f>
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" s="8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C16" s="9" t="n">
-        <f aca="false">Hypothèses!$B$16</f>
-        <v>700</v>
-      </c>
-      <c r="D16" s="9" t="n">
-        <f aca="false">B16*C16</f>
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B18" s="8" t="n">
+      <c r="C24" s="15" t="n">
+        <f aca="false">Hypothèses!$B$32</f>
+        <v>80</v>
+      </c>
+      <c r="D24" s="16" t="n">
+        <f aca="false">B24*C24</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="14" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="C26" s="15" t="n">
         <f aca="false">Hypothèses!$B$8</f>
         <v>500</v>
       </c>
-      <c r="D18" s="9" t="n">
-        <f aca="false">B18*C18</f>
+      <c r="D26" s="16" t="n">
+        <f aca="false">B26*C26</f>
         <v>1500</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B19" s="8" t="n">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B27" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="C19" s="9" t="n">
+      <c r="C27" s="15" t="n">
         <f aca="false">Hypothèses!$B$9</f>
         <v>480</v>
       </c>
-      <c r="D19" s="9" t="n">
-        <f aca="false">B19*C19</f>
+      <c r="D27" s="16" t="n">
+        <f aca="false">B27*C27</f>
         <v>240</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B20" s="8" t="n">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B28" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="C20" s="9" t="n">
+      <c r="C28" s="15" t="n">
         <f aca="false">Hypothèses!$B$10</f>
         <v>480</v>
       </c>
-      <c r="D20" s="9" t="n">
-        <f aca="false">B20*C20</f>
+      <c r="D28" s="16" t="n">
+        <f aca="false">B28*C28</f>
         <v>240</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B21" s="8" t="n">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B29" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C21" s="9" t="n">
+      <c r="C29" s="15" t="n">
         <f aca="false">Hypothèses!$B$11</f>
         <v>600</v>
       </c>
-      <c r="D21" s="9" t="n">
-        <f aca="false">B21*C21</f>
+      <c r="D29" s="16" t="n">
+        <f aca="false">B29*C29</f>
         <v>600</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B22" s="8" t="n">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B30" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C22" s="9" t="n">
+      <c r="C30" s="15" t="n">
         <f aca="false">Hypothèses!$B$8</f>
         <v>500</v>
       </c>
-      <c r="D22" s="9" t="n">
-        <f aca="false">B22*C22</f>
+      <c r="D30" s="16" t="n">
+        <f aca="false">B30*C30</f>
         <v>500</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D23" s="11" t="n">
-        <f aca="false">D3+D4+D5+D6+D8+D9+D10+D11+D12+D13+D14+D15+D16+D18+D19+D20+D21+D22</f>
-        <v>12182.2</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C24" s="12" t="n">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D31" s="16" t="n">
+        <f aca="false">D3+D4+D5+D6+D8+D9+D10+D11+D12+D13+D14+D15+D16+D17+D18+D19+D20+D21+D22+D23+D24+D26+D27+D28+D29+D30</f>
+        <v>21814.944</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C32" s="17" t="n">
         <f aca="false">Hypothèses!$B$18</f>
         <v>0.15</v>
       </c>
-      <c r="D24" s="9" t="n">
-        <f aca="false">D23*Hypothèses!$B$18</f>
-        <v>1827.33</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C25" s="12" t="n">
+      <c r="D32" s="16" t="n">
+        <f aca="false">D31*Hypothèses!$B$18</f>
+        <v>3272.2416</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C33" s="17" t="n">
         <f aca="false">Hypothèses!$B$19</f>
         <v>0.03</v>
       </c>
-      <c r="D25" s="9" t="n">
-        <f aca="false">D23*Hypothèses!$B$19</f>
-        <v>365.466</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C26" s="12" t="n">
+      <c r="D33" s="16" t="n">
+        <f aca="false">D31*Hypothèses!$B$19</f>
+        <v>654.44832</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C34" s="17" t="n">
         <f aca="false">Hypothèses!$B$20</f>
         <v>0.05</v>
       </c>
-      <c r="D26" s="9" t="n">
-        <f aca="false">D23*Hypothèses!$B$20</f>
-        <v>609.11</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D27" s="11" t="n">
-        <f aca="false">D23+D24+D25+D26</f>
-        <v>14984.106</v>
+      <c r="D34" s="16" t="n">
+        <f aca="false">D31*Hypothèses!$B$20</f>
+        <v>1090.7472</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D35" s="16" t="n">
+        <f aca="false">D31+D32+D33+D34</f>
+        <v>26832.38112</v>
       </c>
     </row>
   </sheetData>
@@ -1412,383 +1843,430 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>45</v>
+      <c r="B1" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
-        <v>46</v>
+      <c r="A2" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B3" s="8" t="n">
+      <c r="A3" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="C3" s="9" t="n">
+      <c r="C3" s="15" t="n">
         <f aca="false">Hypothèses!$B$13</f>
         <v>200</v>
       </c>
-      <c r="D3" s="9" t="n">
+      <c r="D3" s="16" t="n">
         <f aca="false">B3*C3</f>
         <v>300</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B4" s="8" t="n">
+      <c r="A4" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="9" t="n">
+      <c r="C4" s="15" t="n">
         <f aca="false">Hypothèses!$B$12</f>
         <v>400</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="16" t="n">
         <f aca="false">B4*C4</f>
         <v>400</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B5" s="8" t="n">
+      <c r="A5" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="15" t="n">
         <f aca="false">Hypothèses!$B$7</f>
         <v>300</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="16" t="n">
         <f aca="false">B5*C5</f>
         <v>150</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B6" s="8" t="n">
+      <c r="A6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="15" t="n">
         <f aca="false">Hypothèses!$B$13</f>
         <v>200</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="16" t="n">
         <f aca="false">B6*C6</f>
         <v>200</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>51</v>
+      <c r="A7" s="14" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B8" s="8" t="n">
+      <c r="A8" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C8" s="15" t="n">
         <f aca="false">Hypothèses!$B$4</f>
         <v>1200</v>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="16" t="n">
         <f aca="false">B8*C8</f>
         <v>1800</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B9" s="8" t="n">
+      <c r="A9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="15" t="n">
         <f aca="false">Hypothèses!$B$5</f>
         <v>550</v>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="D9" s="16" t="n">
         <f aca="false">B9*C9</f>
         <v>825</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="8" t="n">
+      <c r="B10" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="15" t="n">
         <f aca="false">Hypothèses!$B$6</f>
         <v>500</v>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="16" t="n">
         <f aca="false">B10*C10</f>
         <v>750</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B11" s="8" t="n">
+      <c r="A11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="15" t="n">
         <f aca="false">Hypothèses!$B$7</f>
         <v>300</v>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="D11" s="16" t="n">
         <f aca="false">B11*C11</f>
         <v>450</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12" s="8" t="n">
+      <c r="A12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" s="15" t="n">
         <f aca="false">Hypothèses!$B$13</f>
         <v>200</v>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="D12" s="16" t="n">
         <f aca="false">B12*C12</f>
         <v>100</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B13" s="8" t="n">
+      <c r="A13" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C13" s="15" t="n">
         <f aca="false">Hypothèses!$B$14</f>
-        <v>600</v>
-      </c>
-      <c r="D13" s="9" t="n">
+        <v>534</v>
+      </c>
+      <c r="D13" s="16" t="n">
         <f aca="false">B13*C13</f>
-        <v>1800</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C14" s="10" t="n">
+      <c r="A14" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" s="17" t="n">
         <f aca="false">Hypothèses!$B$15</f>
         <v>0.154</v>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="D14" s="16" t="n">
         <f aca="false">D13*C14</f>
-        <v>277.2</v>
+        <v>246.708</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B15" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="9" t="n">
+      <c r="A15" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" s="15" t="n">
         <f aca="false">Hypothèses!$B$17</f>
-        <v>1000</v>
-      </c>
-      <c r="D15" s="9" t="n">
+        <v>90</v>
+      </c>
+      <c r="D15" s="16" t="n">
         <f aca="false">B15*C15</f>
-        <v>1000</v>
+        <v>360</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="C16" s="15" t="n">
+        <f aca="false">Hypothèses!$B$23</f>
+        <v>95</v>
+      </c>
+      <c r="D16" s="16" t="n">
+        <f aca="false">B16*C16</f>
+        <v>760</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="C17" s="15" t="n">
+        <f aca="false">Hypothèses!$B$24</f>
+        <v>40</v>
+      </c>
+      <c r="D17" s="16" t="n">
+        <f aca="false">B17*C17</f>
+        <v>480</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="8" t="n">
+      <c r="B18" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="C16" s="9" t="n">
+      <c r="C18" s="15" t="n">
         <f aca="false">Hypothèses!$B$16</f>
         <v>700</v>
       </c>
-      <c r="D16" s="9" t="n">
-        <f aca="false">B16*C16</f>
+      <c r="D18" s="16" t="n">
+        <f aca="false">B18*C18</f>
         <v>1050</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B18" s="8" t="n">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C19" s="15" t="n">
+        <f aca="false">Hypothèses!$B$25</f>
+        <v>200</v>
+      </c>
+      <c r="D19" s="16" t="n">
+        <f aca="false">B19*C19</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="14" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B21" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="C21" s="15" t="n">
         <f aca="false">Hypothèses!$B$8</f>
         <v>500</v>
       </c>
-      <c r="D18" s="9" t="n">
-        <f aca="false">B18*C18</f>
+      <c r="D21" s="16" t="n">
+        <f aca="false">B21*C21</f>
         <v>1500</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B19" s="8" t="n">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B22" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="C19" s="9" t="n">
+      <c r="C22" s="15" t="n">
         <f aca="false">Hypothèses!$B$9</f>
         <v>480</v>
       </c>
-      <c r="D19" s="9" t="n">
-        <f aca="false">B19*C19</f>
+      <c r="D22" s="16" t="n">
+        <f aca="false">B22*C22</f>
         <v>240</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B20" s="8" t="n">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B23" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="C20" s="9" t="n">
+      <c r="C23" s="15" t="n">
         <f aca="false">Hypothèses!$B$10</f>
         <v>480</v>
       </c>
-      <c r="D20" s="9" t="n">
-        <f aca="false">B20*C20</f>
+      <c r="D23" s="16" t="n">
+        <f aca="false">B23*C23</f>
         <v>240</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B21" s="8" t="n">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B24" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C21" s="9" t="n">
+      <c r="C24" s="15" t="n">
         <f aca="false">Hypothèses!$B$11</f>
         <v>600</v>
       </c>
-      <c r="D21" s="9" t="n">
-        <f aca="false">B21*C21</f>
+      <c r="D24" s="16" t="n">
+        <f aca="false">B24*C24</f>
         <v>600</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B22" s="8" t="n">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B25" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C22" s="9" t="n">
+      <c r="C25" s="15" t="n">
         <f aca="false">Hypothèses!$B$8</f>
         <v>500</v>
       </c>
-      <c r="D22" s="9" t="n">
-        <f aca="false">B22*C22</f>
+      <c r="D25" s="16" t="n">
+        <f aca="false">B25*C25</f>
         <v>500</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D23" s="11" t="n">
-        <f aca="false">D3+D4+D5+D6+D8+D9+D10+D11+D12+D13+D14+D15+D16+D18+D19+D20+D21+D22</f>
-        <v>12182.2</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C24" s="12" t="n">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D26" s="16" t="n">
+        <f aca="false">D3+D4+D5+D6+D8+D9+D10+D11+D12+D13+D14+D15+D16+D17+D18+D19+D21+D22+D23+D24+D25</f>
+        <v>12853.708</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27" s="17" t="n">
         <f aca="false">Hypothèses!$B$18</f>
         <v>0.15</v>
       </c>
-      <c r="D24" s="9" t="n">
-        <f aca="false">D23*Hypothèses!$B$18</f>
-        <v>1827.33</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C25" s="12" t="n">
+      <c r="D27" s="16" t="n">
+        <f aca="false">D26*Hypothèses!$B$18</f>
+        <v>1928.0562</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C28" s="17" t="n">
         <f aca="false">Hypothèses!$B$19</f>
         <v>0.03</v>
       </c>
-      <c r="D25" s="9" t="n">
-        <f aca="false">D23*Hypothèses!$B$19</f>
-        <v>365.466</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C26" s="12" t="n">
+      <c r="D28" s="16" t="n">
+        <f aca="false">D26*Hypothèses!$B$19</f>
+        <v>385.61124</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C29" s="17" t="n">
         <f aca="false">Hypothèses!$B$20</f>
         <v>0.05</v>
       </c>
-      <c r="D26" s="9" t="n">
-        <f aca="false">D23*Hypothèses!$B$20</f>
-        <v>609.11</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D27" s="11" t="n">
-        <f aca="false">D23+D24+D25+D26</f>
-        <v>14984.106</v>
+      <c r="D29" s="16" t="n">
+        <f aca="false">D26*Hypothèses!$B$20</f>
+        <v>642.6854</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D30" s="16" t="n">
+        <f aca="false">D26+D27+D28+D29</f>
+        <v>15810.06084</v>
       </c>
     </row>
   </sheetData>
@@ -1807,82 +2285,1146 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="14" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C3" s="15" t="n">
+        <f aca="false">Hypothèses!$B$13</f>
+        <v>200</v>
+      </c>
+      <c r="D3" s="16" t="n">
+        <f aca="false">B3*C3</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="15" t="n">
+        <f aca="false">Hypothèses!$B$12</f>
+        <v>400</v>
+      </c>
+      <c r="D4" s="16" t="n">
+        <f aca="false">B4*C4</f>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C5" s="15" t="n">
+        <f aca="false">Hypothèses!$B$7</f>
+        <v>300</v>
+      </c>
+      <c r="D5" s="16" t="n">
+        <f aca="false">B5*C5</f>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="15" t="n">
+        <f aca="false">Hypothèses!$B$13</f>
+        <v>200</v>
+      </c>
+      <c r="D6" s="16" t="n">
+        <f aca="false">B6*C6</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14" t="s">
         <v>70</v>
       </c>
     </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="15" t="n">
+        <f aca="false">Hypothèses!$B$4</f>
+        <v>1200</v>
+      </c>
+      <c r="D8" s="16" t="n">
+        <f aca="false">B8*C8</f>
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="15" t="n">
+        <f aca="false">Hypothèses!$B$27</f>
+        <v>450</v>
+      </c>
+      <c r="D9" s="16" t="n">
+        <f aca="false">B9*C9</f>
+        <v>900</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="15" t="n">
+        <f aca="false">Hypothèses!$B$5</f>
+        <v>550</v>
+      </c>
+      <c r="D10" s="16" t="n">
+        <f aca="false">B10*C10</f>
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="15" t="n">
+        <f aca="false">Hypothèses!$B$6</f>
+        <v>500</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <f aca="false">B11*C11</f>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="15" t="n">
+        <f aca="false">Hypothèses!$B$28</f>
+        <v>340</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <f aca="false">B12*C12</f>
+        <v>680</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="15" t="n">
+        <f aca="false">Hypothèses!$B$29</f>
+        <v>430</v>
+      </c>
+      <c r="D13" s="16" t="n">
+        <f aca="false">B13*C13</f>
+        <v>860</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="15" t="n">
+        <f aca="false">Hypothèses!$B$7</f>
+        <v>300</v>
+      </c>
+      <c r="D14" s="16" t="n">
+        <f aca="false">B14*C14</f>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="15" t="n">
+        <f aca="false">Hypothèses!$B$31</f>
+        <v>400</v>
+      </c>
+      <c r="D15" s="16" t="n">
+        <f aca="false">B15*C15</f>
+        <v>800</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="15" t="n">
+        <f aca="false">Hypothèses!$B$13</f>
+        <v>200</v>
+      </c>
+      <c r="D16" s="16" t="n">
+        <f aca="false">B16*C16</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" s="15" t="n">
+        <f aca="false">Hypothèses!$B$14</f>
+        <v>534</v>
+      </c>
+      <c r="D17" s="16" t="n">
+        <f aca="false">B17*C17</f>
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" s="17" t="n">
+        <f aca="false">Hypothèses!$B$15</f>
+        <v>0.154</v>
+      </c>
+      <c r="D18" s="16" t="n">
+        <f aca="false">D17*C18</f>
+        <v>328.944</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="C19" s="15" t="n">
+        <f aca="false">Hypothèses!$B$17</f>
+        <v>90</v>
+      </c>
+      <c r="D19" s="16" t="n">
+        <f aca="false">B19*C19</f>
+        <v>720</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="C20" s="15" t="n">
+        <f aca="false">Hypothèses!$B$23</f>
+        <v>95</v>
+      </c>
+      <c r="D20" s="16" t="n">
+        <f aca="false">B20*C20</f>
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="C21" s="15" t="n">
+        <f aca="false">Hypothèses!$B$24</f>
+        <v>40</v>
+      </c>
+      <c r="D21" s="16" t="n">
+        <f aca="false">B21*C21</f>
+        <v>960</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" s="15" t="n">
+        <f aca="false">Hypothèses!$B$30</f>
+        <v>1500</v>
+      </c>
+      <c r="D22" s="16" t="n">
+        <f aca="false">B22*C22</f>
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" s="15" t="n">
+        <f aca="false">Hypothèses!$B$25</f>
+        <v>200</v>
+      </c>
+      <c r="D23" s="16" t="n">
+        <f aca="false">B23*C23</f>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="15" t="n">
+        <f aca="false">Hypothèses!$B$32</f>
+        <v>80</v>
+      </c>
+      <c r="D24" s="16" t="n">
+        <f aca="false">B24*C24</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="14" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" s="15" t="n">
+        <f aca="false">Hypothèses!$B$8</f>
+        <v>500</v>
+      </c>
+      <c r="D26" s="16" t="n">
+        <f aca="false">B26*C26</f>
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C27" s="15" t="n">
+        <f aca="false">Hypothèses!$B$9</f>
+        <v>480</v>
+      </c>
+      <c r="D27" s="16" t="n">
+        <f aca="false">B27*C27</f>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C28" s="15" t="n">
+        <f aca="false">Hypothèses!$B$10</f>
+        <v>480</v>
+      </c>
+      <c r="D28" s="16" t="n">
+        <f aca="false">B28*C28</f>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="15" t="n">
+        <f aca="false">Hypothèses!$B$11</f>
+        <v>600</v>
+      </c>
+      <c r="D29" s="16" t="n">
+        <f aca="false">B29*C29</f>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="15" t="n">
+        <f aca="false">Hypothèses!$B$8</f>
+        <v>500</v>
+      </c>
+      <c r="D30" s="16" t="n">
+        <f aca="false">B30*C30</f>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D31" s="16" t="n">
+        <f aca="false">D3+D4+D5+D6+D8+D9+D10+D11+D12+D13+D14+D15+D16+D17+D18+D19+D20+D21+D22+D23+D24+D26+D27+D28+D29+D30</f>
+        <v>21814.944</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C32" s="17" t="n">
+        <f aca="false">Hypothèses!$B$18</f>
+        <v>0.15</v>
+      </c>
+      <c r="D32" s="16" t="n">
+        <f aca="false">D31*Hypothèses!$B$18</f>
+        <v>3272.2416</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C33" s="17" t="n">
+        <f aca="false">Hypothèses!$B$19</f>
+        <v>0.03</v>
+      </c>
+      <c r="D33" s="16" t="n">
+        <f aca="false">D31*Hypothèses!$B$19</f>
+        <v>654.44832</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C34" s="17" t="n">
+        <f aca="false">Hypothèses!$B$20</f>
+        <v>0.05</v>
+      </c>
+      <c r="D34" s="16" t="n">
+        <f aca="false">D31*Hypothèses!$B$20</f>
+        <v>1090.7472</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D35" s="16" t="n">
+        <f aca="false">D31+D32+D33+D34</f>
+        <v>26832.38112</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D30"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>64</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="14" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C3" s="15" t="n">
+        <f aca="false">Hypothèses!$B$13</f>
+        <v>200</v>
+      </c>
+      <c r="D3" s="16" t="n">
+        <f aca="false">B3*C3</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="15" t="n">
+        <f aca="false">Hypothèses!$B$12</f>
+        <v>400</v>
+      </c>
+      <c r="D4" s="16" t="n">
+        <f aca="false">B4*C4</f>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C5" s="15" t="n">
+        <f aca="false">Hypothèses!$B$7</f>
+        <v>300</v>
+      </c>
+      <c r="D5" s="16" t="n">
+        <f aca="false">B5*C5</f>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="15" t="n">
+        <f aca="false">Hypothèses!$B$13</f>
+        <v>200</v>
+      </c>
+      <c r="D6" s="16" t="n">
+        <f aca="false">B6*C6</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C8" s="15" t="n">
+        <f aca="false">Hypothèses!$B$4</f>
+        <v>1200</v>
+      </c>
+      <c r="D8" s="16" t="n">
+        <f aca="false">B8*C8</f>
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C9" s="15" t="n">
+        <f aca="false">Hypothèses!$B$5</f>
+        <v>550</v>
+      </c>
+      <c r="D9" s="16" t="n">
+        <f aca="false">B9*C9</f>
+        <v>825</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C10" s="15" t="n">
+        <f aca="false">Hypothèses!$B$6</f>
+        <v>500</v>
+      </c>
+      <c r="D10" s="16" t="n">
+        <f aca="false">B10*C10</f>
+        <v>750</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C11" s="15" t="n">
+        <f aca="false">Hypothèses!$B$7</f>
+        <v>300</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <f aca="false">B11*C11</f>
+        <v>450</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C12" s="15" t="n">
+        <f aca="false">Hypothèses!$B$13</f>
+        <v>200</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <f aca="false">B12*C12</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="15" t="n">
+        <f aca="false">Hypothèses!$B$14</f>
+        <v>534</v>
+      </c>
+      <c r="D13" s="16" t="n">
+        <f aca="false">B13*C13</f>
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" s="17" t="n">
+        <f aca="false">Hypothèses!$B$15</f>
+        <v>0.154</v>
+      </c>
+      <c r="D14" s="16" t="n">
+        <f aca="false">D13*C14</f>
+        <v>246.708</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" s="15" t="n">
+        <f aca="false">Hypothèses!$B$17</f>
+        <v>90</v>
+      </c>
+      <c r="D15" s="16" t="n">
+        <f aca="false">B15*C15</f>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="C16" s="15" t="n">
+        <f aca="false">Hypothèses!$B$23</f>
+        <v>95</v>
+      </c>
+      <c r="D16" s="16" t="n">
+        <f aca="false">B16*C16</f>
+        <v>760</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="C17" s="15" t="n">
+        <f aca="false">Hypothèses!$B$24</f>
+        <v>40</v>
+      </c>
+      <c r="D17" s="16" t="n">
+        <f aca="false">B17*C17</f>
+        <v>480</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C18" s="15" t="n">
+        <f aca="false">Hypothèses!$B$16</f>
+        <v>700</v>
+      </c>
+      <c r="D18" s="16" t="n">
+        <f aca="false">B18*C18</f>
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C19" s="15" t="n">
+        <f aca="false">Hypothèses!$B$25</f>
+        <v>200</v>
+      </c>
+      <c r="D19" s="16" t="n">
+        <f aca="false">B19*C19</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="14" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" s="15" t="n">
+        <f aca="false">Hypothèses!$B$8</f>
+        <v>500</v>
+      </c>
+      <c r="D21" s="16" t="n">
+        <f aca="false">B21*C21</f>
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C22" s="15" t="n">
+        <f aca="false">Hypothèses!$B$9</f>
+        <v>480</v>
+      </c>
+      <c r="D22" s="16" t="n">
+        <f aca="false">B22*C22</f>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C23" s="15" t="n">
+        <f aca="false">Hypothèses!$B$10</f>
+        <v>480</v>
+      </c>
+      <c r="D23" s="16" t="n">
+        <f aca="false">B23*C23</f>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="15" t="n">
+        <f aca="false">Hypothèses!$B$11</f>
+        <v>600</v>
+      </c>
+      <c r="D24" s="16" t="n">
+        <f aca="false">B24*C24</f>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="15" t="n">
+        <f aca="false">Hypothèses!$B$8</f>
+        <v>500</v>
+      </c>
+      <c r="D25" s="16" t="n">
+        <f aca="false">B25*C25</f>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D26" s="16" t="n">
+        <f aca="false">D3+D4+D5+D6+D8+D9+D10+D11+D12+D13+D14+D15+D16+D17+D18+D19+D21+D22+D23+D24+D25</f>
+        <v>12853.708</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27" s="17" t="n">
+        <f aca="false">Hypothèses!$B$18</f>
+        <v>0.15</v>
+      </c>
+      <c r="D27" s="16" t="n">
+        <f aca="false">D26*Hypothèses!$B$18</f>
+        <v>1928.0562</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C28" s="17" t="n">
+        <f aca="false">Hypothèses!$B$19</f>
+        <v>0.03</v>
+      </c>
+      <c r="D28" s="16" t="n">
+        <f aca="false">D26*Hypothèses!$B$19</f>
+        <v>385.61124</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C29" s="17" t="n">
+        <f aca="false">Hypothèses!$B$20</f>
+        <v>0.05</v>
+      </c>
+      <c r="D29" s="16" t="n">
+        <f aca="false">D26*Hypothèses!$B$20</f>
+        <v>642.6854</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D30" s="16" t="n">
+        <f aca="false">D26+D27+D28+D29</f>
+        <v>15810.06084</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B23"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B2" s="9" t="n">
-        <f aca="false">CYRCE!D27</f>
-        <v>14984.106</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B3" s="9" t="n">
-        <f aca="false">BIOT2!D27</f>
-        <v>14984.106</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B4" s="11" t="n">
-        <f aca="false">B2+B3</f>
-        <v>29968.212</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B2" s="18"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B3" s="19" t="n">
+        <f aca="false">CYRCE_A!D35</f>
+        <v>26832.38112</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="B4" s="21" t="n">
+        <f aca="false">BIOT2_A!D35</f>
+        <v>26832.38112</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="B5" s="21" t="n">
+        <f aca="false">B3+B4</f>
+        <v>53664.76224</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="9" t="n">
-        <f aca="false">B4*Hypothèses!$B$21</f>
-        <v>5993.6424</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="B6" s="11" t="n">
-        <f aca="false">B4+B5</f>
-        <v>35961.8544</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="B6" s="21" t="n">
+        <f aca="false">B5*Hypothèses!$B$21</f>
+        <v>10732.952448</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" s="21" t="n">
+        <f aca="false">B5+B6</f>
+        <v>64397.714688</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="20"/>
+      <c r="B8" s="21"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="B9" s="22"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B10" s="16" t="n">
+        <f aca="false">CYRCE_B!D30</f>
+        <v>15810.06084</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B11" s="16" t="n">
+        <f aca="false">BIOT2_B!D30</f>
+        <v>15810.06084</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="B12" s="23" t="n">
+        <f aca="false">B10+B11</f>
+        <v>31620.12168</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="16" t="n">
+        <f aca="false">B12*Hypothèses!$B$21</f>
+        <v>6324.024336</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="B14" s="23" t="n">
+        <f aca="false">B12+B13</f>
+        <v>37944.146016</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="B16" s="22"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="9" t="n">
+      <c r="B17" s="16" t="n">
         <f aca="false">Hypothèses!$B$22</f>
         <v>40000</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="B8" s="11" t="n">
-        <f aca="false">B7-B6</f>
-        <v>4038.1456</v>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="B18" s="23" t="n">
+        <f aca="false">B17-B14</f>
+        <v>2055.853984</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B20" s="22"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="B21" s="23" t="n">
+        <f aca="false">B5-B12</f>
+        <v>22044.64056</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="B22" s="23" t="n">
+        <f aca="false">B7-B14</f>
+        <v>26453.568672</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B23" s="24" t="n">
+        <f aca="false">B21/B5</f>
+        <v>0.410784277053382</v>
       </c>
     </row>
   </sheetData>
